--- a/docs/lab1/source/计算机23-2_231002208_戚晋瑜_实验一_RequirementsList_v1.0.xlsx
+++ b/docs/lab1/source/计算机23-2_231002208_戚晋瑜_实验一_RequirementsList_v1.0.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="功能需求" sheetId="1" r:id="Rdfb6478292a94960"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能需求" sheetId="2" r:id="R606388a7ea454335"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求统计" sheetId="3" r:id="R54442091d67c49f2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="功能需求" sheetId="1" r:id="R4f297d54f2cd49b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能需求" sheetId="2" r:id="R1c8ffd4369114e38"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求统计" sheetId="3" r:id="R85fcd56173f4467d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1596,7 +1596,7 @@
         <x:v>NFR-005</x:v>
       </x:c>
       <x:c r="B6" s="5" t="str">
-        <x:v>可用性</x:v>
+        <x:v>易用性</x:v>
       </x:c>
       <x:c r="C6" s="5" t="str">
         <x:v>顾客端关键流程在移动端三步内完成预约</x:v>
@@ -1660,7 +1660,7 @@
         <x:v>NFR-007</x:v>
       </x:c>
       <x:c r="B8" s="5" t="str">
-        <x:v>可审计性</x:v>
+        <x:v>安全性</x:v>
       </x:c>
       <x:c r="C8" s="5" t="str">
         <x:v>关键运营操作需保留不少于 180 天的审计日志</x:v>
@@ -1724,7 +1724,7 @@
         <x:v>NFR-009</x:v>
       </x:c>
       <x:c r="B10" s="5" t="str">
-        <x:v>功能适应性</x:v>
+        <x:v>功能适合性</x:v>
       </x:c>
       <x:c r="C10" s="5" t="str">
         <x:v>推荐结果需在 2 秒内返回并说明原因</x:v>
